--- a/InoRobotSelect/Robot_spec.xlsx
+++ b/InoRobotSelect/Robot_spec.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="323" documentId="8_{522FA3AE-843B-45F5-9EBE-713FE4E8C55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E12D8BA1-58AD-432E-AC83-292119DE4DDD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{166C1812-565C-44F3-A85A-A23A1F110762}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{166C1812-565C-44F3-A85A-A23A1F110762}"/>
   </bookViews>
   <sheets>
     <sheet name="6-Axis" sheetId="3" r:id="rId1"/>
